--- a/excel_upload_masters/templates/16_ingestion_audit.xlsx
+++ b/excel_upload_masters/templates/16_ingestion_audit.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingestion_events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ingestion_events" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,6 +433,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>express</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pro_inspect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pro_confirm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sla</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>revenue_trackers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -502,13 +586,29 @@
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="E3:E5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$B$1:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>